--- a/output/roomself_excel/3736.xlsx
+++ b/output/roomself_excel/3736.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>102446</v>
+        <v>105444</v>
       </c>
       <c r="D2" t="n">
-        <v>2580</v>
+        <v>2604</v>
       </c>
       <c r="E2" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F2" t="n">
-        <v>295</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3">
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>425638</v>
+        <v>307978</v>
       </c>
       <c r="D3" t="n">
-        <v>8324</v>
+        <v>4596</v>
       </c>
       <c r="E3" t="n">
-        <v>1127</v>
+        <v>743</v>
       </c>
       <c r="F3" t="n">
         <v>471</v>
@@ -510,14 +510,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>168880</v>
+        <v>62988</v>
       </c>
       <c r="D4" t="n">
-        <v>3536</v>
+        <v>2028</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>115188</v>
+        <v>102446</v>
       </c>
       <c r="D5" t="n">
-        <v>2716</v>
+        <v>2580</v>
       </c>
       <c r="E5" t="n">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72384</v>
+        <v>168880</v>
       </c>
       <c r="D6" t="n">
-        <v>2224</v>
+        <v>3536</v>
       </c>
       <c r="E6" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>107880</v>
+        <v>115188</v>
       </c>
       <c r="D7" t="n">
-        <v>2632</v>
+        <v>2716</v>
       </c>
       <c r="E7" t="n">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="F7" t="n">
         <v>22</v>
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18360</v>
+        <v>72384</v>
       </c>
       <c r="D8" t="n">
-        <v>1128</v>
+        <v>2224</v>
       </c>
       <c r="E8" t="n">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>105444</v>
+        <v>107880</v>
       </c>
       <c r="D9" t="n">
-        <v>2604</v>
+        <v>2632</v>
       </c>
       <c r="E9" t="n">
-        <v>371</v>
+        <v>310</v>
       </c>
       <c r="F9" t="n">
-        <v>325</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>42720</v>
+        <v>54672</v>
       </c>
       <c r="D10" t="n">
-        <v>1672</v>
+        <v>2552</v>
       </c>
       <c r="E10" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>44235</v>
+        <v>18360</v>
       </c>
       <c r="D11" t="n">
-        <v>1812</v>
+        <v>1128</v>
       </c>
       <c r="E11" t="n">
-        <v>213</v>
+        <v>102</v>
       </c>
       <c r="F11" t="n">
         <v>23</v>
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>76828</v>
+        <v>42720</v>
       </c>
       <c r="D12" t="n">
-        <v>2432</v>
+        <v>1672</v>
       </c>
       <c r="E12" t="n">
-        <v>334</v>
+        <v>178</v>
       </c>
       <c r="F12" t="n">
-        <v>263</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12876</v>
+        <v>44235</v>
       </c>
       <c r="D13" t="n">
-        <v>908</v>
+        <v>1812</v>
       </c>
       <c r="E13" t="n">
-        <v>116</v>
+        <v>213</v>
       </c>
       <c r="F13" t="n">
         <v>23</v>
@@ -734,15 +734,59 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>76828</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2432</v>
+      </c>
+      <c r="E14" t="n">
+        <v>323</v>
+      </c>
+      <c r="F14" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12876</v>
+      </c>
+      <c r="D15" t="n">
+        <v>908</v>
+      </c>
+      <c r="E15" t="n">
+        <v>116</v>
+      </c>
+      <c r="F15" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>15651</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D16" t="n">
         <v>1008</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E16" t="n">
         <v>141</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F16" t="n">
         <v>23</v>
       </c>
     </row>

--- a/output/roomself_excel/3736.xlsx
+++ b/output/roomself_excel/3736.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>2604</v>
       </c>
-      <c r="E2" t="n">
-        <v>371</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>325</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>303</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>4596</v>
       </c>
-      <c r="E3" t="n">
-        <v>743</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>471</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1067</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,15 @@
       <c r="D4" t="n">
         <v>2028</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +617,38 @@
       <c r="D5" t="n">
         <v>2580</v>
       </c>
-      <c r="E5" t="n">
-        <v>374</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>295</v>
+        <v>283</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>362</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>362</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +666,23 @@
       <c r="D6" t="n">
         <v>3536</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +699,23 @@
       <c r="D7" t="n">
         <v>2716</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>322</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>22</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +732,23 @@
       <c r="D8" t="n">
         <v>2224</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>208</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>22</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +765,23 @@
       <c r="D9" t="n">
         <v>2632</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>310</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>22</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +798,15 @@
       <c r="D10" t="n">
         <v>2552</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +823,23 @@
       <c r="D11" t="n">
         <v>1128</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>102</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>23</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +856,23 @@
       <c r="D12" t="n">
         <v>1672</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>178</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>23</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +889,23 @@
       <c r="D13" t="n">
         <v>1812</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>213</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>23</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +922,31 @@
       <c r="D14" t="n">
         <v>2432</v>
       </c>
-      <c r="E14" t="n">
-        <v>323</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>263</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="G14" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>300</v>
+      </c>
+      <c r="J14" t="n">
+        <v>23</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +963,23 @@
       <c r="D15" t="n">
         <v>908</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>116</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>23</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +996,23 @@
       <c r="D16" t="n">
         <v>1008</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>141</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>23</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
